--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -1,179 +1,338 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="dialog_meta_info" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="144525" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+  <si>
+    <t>##var</t>
+  </si>
+  <si>
+    <t>dialog_id</t>
+  </si>
+  <si>
+    <t>##comment</t>
+  </si>
+  <si>
+    <t>is_auto_trigger</t>
+  </si>
+  <si>
+    <t>only_once</t>
+  </si>
+  <si>
+    <t>json_data_name</t>
+  </si>
+  <si>
+    <t>need_map</t>
+  </si>
+  <si>
+    <t>trigger_cond</t>
+  </si>
+  <si>
+    <t>active_trigger_npc</t>
+  </si>
+  <si>
+    <t>lock_global_time</t>
+  </si>
+  <si>
+    <t>controlled_entity_list</t>
+  </si>
+  <si>
+    <t>show_priority</t>
+  </si>
+  <si>
+    <t>custom_variables</t>
+  </si>
+  <si>
+    <t>cutscene_id</t>
+  </si>
+  <si>
+    <t>##type</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>(list#sep=;),CommonCheckCond</t>
+  </si>
+  <si>
+    <t>(list#sep=;),string</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>(map#sep=,|),string,string</t>
+  </si>
+  <si>
+    <t>##group</t>
+  </si>
+  <si>
+    <t>c,s</t>
+  </si>
+  <si>
+    <t>##</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>是否自动触发</t>
+  </si>
+  <si>
+    <t>是否唯一</t>
+  </si>
+  <si>
+    <t>数据路径</t>
+  </si>
+  <si>
+    <t>触发地图</t>
+  </si>
+  <si>
+    <t>触发条件</t>
+  </si>
+  <si>
+    <t>触发npc</t>
+  </si>
+  <si>
+    <t>是否全局时停</t>
+  </si>
+  <si>
+    <t>控制列表
+键为单位唯一名</t>
+  </si>
+  <si>
+    <t>显示优先级
+npc始终绑定只一个普通对话，按照优先级排序</t>
+  </si>
+  <si>
+    <t>传参入口
+用于对白数据复用</t>
+  </si>
+  <si>
+    <t>特殊演出地图
+该值有值时会进行场景切换</t>
+  </si>
+  <si>
+    <t>init_dialog_01</t>
+  </si>
+  <si>
+    <t>出门加载第一段</t>
+  </si>
+  <si>
+    <t>game_init</t>
+  </si>
+  <si>
+    <t>init_luca</t>
+  </si>
+  <si>
+    <t>base_fight_end</t>
+  </si>
+  <si>
+    <t>出门战斗结束</t>
+  </si>
+  <si>
+    <t>TaskFinish,100,0,0,0,0,0</t>
+  </si>
+  <si>
+    <t>scene_base_fight_end_show</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
   <fonts count="20">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -473,157 +632,163 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -678,74 +843,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -997,43 +1099,275 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:O7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <cols>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="3" max="3" width="26.25" customWidth="1"/>
+    <col min="4" max="7" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="13.875" customWidth="1"/>
+    <col min="9" max="9" width="13.375" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="12" width="20.5" customWidth="1"/>
+    <col min="13" max="13" width="26.125" customWidth="1"/>
+    <col min="14" max="14" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="1"/>
+    </row>
+    <row r="4" ht="67.5" spans="1:15">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="N7" t="s">
+        <v>43</v>
+      </c>
+      <c r="O7" s="1"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -161,7 +161,10 @@
     <t>出门战斗结束</t>
   </si>
   <si>
-    <t>TaskFinish,100,0,0,0,0,0</t>
+    <t>base_fight</t>
+  </si>
+  <si>
+    <t>TaskFinish,101,0,0,0,0,0</t>
   </si>
   <si>
     <t>scene_base_fight_end_show</t>
@@ -1307,8 +1310,6 @@
       <c r="G5" t="s">
         <v>38</v>
       </c>
-      <c r="H5"/>
-      <c r="I5"/>
       <c r="K5" t="s">
         <v>39</v>
       </c>
@@ -1316,6 +1317,7 @@
     <row r="6" spans="1:15">
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:15">
       <c r="B7" s="1" t="s">
@@ -1333,11 +1335,14 @@
       <c r="F7" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="G7" t="s">
+        <v>42</v>
+      </c>
       <c r="H7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O7" s="1"/>
     </row>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -4,11 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17655" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="dialog_meta_info" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="npc_dialog_info" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="59">
   <si>
     <t>##var</t>
   </si>
@@ -168,6 +168,48 @@
   </si>
   <si>
     <t>scene_base_fight_end_show</t>
+  </si>
+  <si>
+    <t>game_init_luca_injured_01</t>
+  </si>
+  <si>
+    <t>game_init_luca_injured_02</t>
+  </si>
+  <si>
+    <t>game_init_luca_injured_03</t>
+  </si>
+  <si>
+    <t>npc_id</t>
+  </si>
+  <si>
+    <t>priority</t>
+  </si>
+  <si>
+    <t>show_cond</t>
+  </si>
+  <si>
+    <t>need_npc_val</t>
+  </si>
+  <si>
+    <t>npcId</t>
+  </si>
+  <si>
+    <t>对话id</t>
+  </si>
+  <si>
+    <t>解锁条件</t>
+  </si>
+  <si>
+    <t>所需标记</t>
+  </si>
+  <si>
+    <t>game_init_luca_injured</t>
+  </si>
+  <si>
+    <t>CheckVariable,0,0,0,0,init.dialog_01,0</t>
+  </si>
+  <si>
+    <t>TaskFinish,100,0,0,0,0,0</t>
   </si>
 </sst>
 </file>
@@ -1104,8 +1146,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:O7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="26.25" customWidth="1"/>
@@ -1346,6 +1388,21 @@
       </c>
       <c r="O7" s="1"/>
     </row>
+    <row r="9" spans="1:15">
+      <c r="B9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="B11" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1356,9 +1413,160 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="5" max="5" width="9.5" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="B7" s="1">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17655" activeTab="1"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="dialog_meta_info" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -204,12 +204,6 @@
   </si>
   <si>
     <t>game_init_luca_injured</t>
-  </si>
-  <si>
-    <t>CheckVariable,0,0,0,0,init.dialog_01,0</t>
-  </si>
-  <si>
-    <t>TaskFinish,100,0,0,0,0,0</t>
   </si>
 </sst>
 </file>
@@ -1149,7 +1143,7 @@
   <dimension ref="A1:O11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="16.75" customWidth="1"/>
+    <col min="2" max="2" width="40.625" customWidth="1"/>
     <col min="3" max="3" width="26.25" customWidth="1"/>
     <col min="4" max="7" width="13.5" customWidth="1"/>
     <col min="8" max="8" width="13.875" customWidth="1"/>
@@ -1392,14 +1386,23 @@
       <c r="B9" t="s">
         <v>45</v>
       </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="B10" t="s">
         <v>46</v>
       </c>
+      <c r="F10" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="B11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1417,8 +1420,8 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
-    <col min="4" max="4" width="17.375" customWidth="1"/>
+    <col min="3" max="3" width="27.75" customWidth="1"/>
+    <col min="4" max="4" width="53.75" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
     <col min="6" max="6" width="13.75" customWidth="1"/>
   </cols>
@@ -1528,9 +1531,6 @@
       <c r="E5">
         <v>1</v>
       </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
     </row>
     <row r="6" spans="1:7">
       <c r="B6" s="1">
@@ -1545,9 +1545,6 @@
       <c r="E6">
         <v>2</v>
       </c>
-      <c r="F6" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="7" spans="1:7">
       <c r="B7" s="1">
@@ -1561,9 +1558,6 @@
       </c>
       <c r="E7">
         <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="61">
   <si>
     <t>##var</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>player_gouyin</t>
+  </si>
+  <si>
+    <t>qigai_01</t>
   </si>
   <si>
     <t>npc_id</t>
@@ -1147,7 +1150,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="40.625" style="1" customWidth="1"/>
@@ -1450,6 +1453,23 @@
         <v>50</v>
       </c>
       <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="J15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1481,19 +1501,19 @@
         <v>24</v>
       </c>
       <c r="C1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D1" t="s">
         <v>1</v>
       </c>
       <c r="E1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1550,19 +1570,19 @@
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1570,7 +1590,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" t="s">
         <v>45</v>
@@ -1584,7 +1604,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6" t="s">
         <v>46</v>
@@ -1598,7 +1618,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" t="s">
         <v>47</v>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -9,6 +9,7 @@
     <sheet name="dialog_meta_info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="npc_dialog_info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="quest_interact_dialog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1302,652 +1303,652 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>init_dialog_01</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>开场教程第一句</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="b">
+      <c r="E5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>init_dialog_01</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>game_init</t>
         </is>
       </c>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
+      <c r="J5" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="inlineStr">
         <is>
           <t>init_luca</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>base_fight_end</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>基地战斗结束</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="b">
+      <c r="E6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>base_fight_end</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>base_fight</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>1,101,0,0,0,0,0</t>
         </is>
       </c>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
+      <c r="J6" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0" t="inlineStr">
         <is>
           <t>scene_base_fight_end_show</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_01</t>
         </is>
       </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_01</t>
         </is>
       </c>
-      <c r="J7" t="b">
+      <c r="J7" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_02</t>
         </is>
       </c>
-      <c r="D8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" t="b">
-        <v>0</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_02</t>
         </is>
       </c>
-      <c r="J8" t="b">
+      <c r="J8" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_03</t>
         </is>
       </c>
-      <c r="D9" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" t="b">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="D9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>game_init_luca_injured_03</t>
         </is>
       </c>
-      <c r="J9" t="b">
+      <c r="J9" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>npc_generic_entry</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>NPC动态Hub入口</t>
         </is>
       </c>
-      <c r="D10" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>npc_generic_entry</t>
         </is>
       </c>
-      <c r="J10" t="b">
+      <c r="J10" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>player_gouyin</t>
         </is>
       </c>
-      <c r="D11" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="D11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>player_gouyin</t>
         </is>
       </c>
-      <c r="J11" t="b">
+      <c r="J11" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>qigai_01</t>
         </is>
       </c>
-      <c r="D12" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>qigai_01</t>
         </is>
       </c>
-      <c r="J12" t="b">
+      <c r="J12" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>npc_quest_accept_ok</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>任务接取成功fallback</t>
         </is>
       </c>
-      <c r="D13" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>npc_quest_accept_ok</t>
         </is>
       </c>
-      <c r="J13" t="b">
+      <c r="J13" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>npc_quest_accept_fail</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>任务接取失败fallback</t>
         </is>
       </c>
-      <c r="D14" t="b">
-        <v>0</v>
-      </c>
-      <c r="E14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E14" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>npc_quest_accept_fail</t>
         </is>
       </c>
-      <c r="J14" t="b">
+      <c r="J14" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>npc_quest_fulfill_ok</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>任务交付成功fallback</t>
         </is>
       </c>
-      <c r="D15" t="b">
-        <v>0</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E15" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>npc_quest_fulfill_ok</t>
         </is>
       </c>
-      <c r="J15" t="b">
+      <c r="J15" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>npc_quest_fulfill_fail</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>任务交付失败fallback</t>
         </is>
       </c>
-      <c r="D16" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" t="inlineStr">
+      <c r="D16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>npc_quest_fulfill_fail</t>
         </is>
       </c>
-      <c r="J16" t="b">
+      <c r="J16" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>homestead_remind_herb</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>任务200复述</t>
         </is>
       </c>
-      <c r="D17" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="inlineStr">
+      <c r="D17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>homestead_remind_herb</t>
         </is>
       </c>
-      <c r="J17" t="b">
+      <c r="J17" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_entry</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>任务200交付入口</t>
         </is>
       </c>
-      <c r="D18" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" t="b">
-        <v>0</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_entry</t>
         </is>
       </c>
-      <c r="J18" t="b">
+      <c r="J18" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_ok</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>任务200交付成功</t>
         </is>
       </c>
-      <c r="D19" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="inlineStr">
+      <c r="D19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_ok</t>
         </is>
       </c>
-      <c r="J19" t="b">
+      <c r="J19" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_fail</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>任务200交付失败</t>
         </is>
       </c>
-      <c r="D20" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_herb_fail</t>
         </is>
       </c>
-      <c r="J20" t="b">
+      <c r="J20" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>任务201接取入口</t>
         </is>
       </c>
-      <c r="D21" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="inlineStr">
+      <c r="D21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood</t>
         </is>
       </c>
-      <c r="J21" t="b">
+      <c r="J21" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood_ok</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>任务201接取成功</t>
         </is>
       </c>
-      <c r="D22" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="inlineStr">
+      <c r="D22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood_ok</t>
         </is>
       </c>
-      <c r="J22" t="b">
+      <c r="J22" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood_fail</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>任务201接取失败</t>
         </is>
       </c>
-      <c r="D23" t="b">
-        <v>0</v>
-      </c>
-      <c r="E23" t="b">
-        <v>0</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="D23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E23" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>homestead_accept_wood_fail</t>
         </is>
       </c>
-      <c r="J23" t="b">
+      <c r="J23" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>homestead_remind_wood</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>任务201复述</t>
         </is>
       </c>
-      <c r="D24" t="b">
-        <v>0</v>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>homestead_remind_wood</t>
         </is>
       </c>
-      <c r="J24" t="b">
+      <c r="J24" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_entry</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>任务201交付入口</t>
         </is>
       </c>
-      <c r="D25" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" t="b">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="D25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_entry</t>
         </is>
       </c>
-      <c r="J25" t="b">
+      <c r="J25" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_ok</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>任务201交付成功</t>
         </is>
       </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" t="b">
-        <v>0</v>
-      </c>
-      <c r="F26" t="inlineStr">
+      <c r="D26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_ok</t>
         </is>
       </c>
-      <c r="J26" t="b">
+      <c r="J26" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_fail</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>任务201交付失败</t>
         </is>
       </c>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="inlineStr">
+      <c r="D27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>homestead_submit_wood_fail</t>
         </is>
       </c>
-      <c r="J27" t="b">
+      <c r="J27" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>homestead_elder_01</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>镇长和平对话</t>
         </is>
       </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
+      <c r="D28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>homestead_elder_01</t>
         </is>
       </c>
-      <c r="J28" t="b">
+      <c r="J28" s="0" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>homestead_merchant_01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>木匠和平对话</t>
         </is>
       </c>
-      <c r="D29" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" t="inlineStr">
+      <c r="D29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>homestead_merchant_01</t>
         </is>
       </c>
-      <c r="J29" t="b">
+      <c r="J29" s="0" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2193,4 +2194,617 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>quest_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>obj_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dialog_role</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>dialog_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>option_text</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>show_cond</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EQuestDialogRole</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),CommonCheckCond</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>任务 id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Remind 匹配 step_id</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>递交目标 obj_id</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>NPC CharacterKey</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>对话角色</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>对话 id</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Hub 选项文案</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>显示条件</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>排序优先级</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>200</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>200_s1</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>homestead_remind_herb</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>我还该做什么？</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>200</v>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>200_s2_Main</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>homestead_submit_herb_entry</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>这些草药给你。</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>200</v>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>200_s2_Main</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>homestead_submit_herb_ok</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>200</v>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>200_s2_Main</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>FulfillFail</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>homestead_submit_herb_fail</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>201</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>homestead_accept_wood</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>关于采集木材……</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>201</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>AcceptSuccess</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>homestead_accept_wood_ok</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>201</v>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>AcceptFail</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>homestead_accept_wood_fail</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>201</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>201_s1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>homestead_remind_wood</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>我还该做什么？</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>201</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>201_s2_Main</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>homestead_submit_wood_entry</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>这些木材给你。</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>201</v>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>201_s2_Main</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>homestead_submit_wood_ok</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" t="n">
+        <v>201</v>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>201_s2_Main</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>FulfillFail</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>homestead_submit_wood_fail</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="40.625" customWidth="1" style="1" min="2" max="2"/>
@@ -2124,6 +2124,742 @@
         <v>0</v>
       </c>
     </row>
+    <row r="35" s="1">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>forest_gujou_reunion</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>森林废墟咕啾重逢</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>forest_gujou_reunion</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>forest_01</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="L35" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="36" s="1">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>game_init_lilith_wakeup_tutorial</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>开场新手引导：莉莉丝在地牢醒来</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>game_init_lilith_wakeup_tutorial</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>game_init</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="L36" s="0" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" s="1">
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>game_init_after_first_monsters</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>开场新手引导：击退怪物后发现卡莱尔</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>game_init_after_first_monsters</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>game_init</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,100,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="L37" s="0" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" s="1">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_entry</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔昏迷状态交互入口</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_entry</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="n"/>
+      <c r="J38" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" s="0" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" s="1">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_first_check</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>首次检查昏迷的卡莱尔</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_first_check</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="n"/>
+      <c r="J39" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L39" s="0" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" s="1">
+      <c r="B40" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid</t>
+        </is>
+      </c>
+      <c r="C40" s="0" t="inlineStr">
+        <is>
+          <t>任务300接取入口：临时包扎</t>
+        </is>
+      </c>
+      <c r="D40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid</t>
+        </is>
+      </c>
+      <c r="G40" s="0" t="n"/>
+      <c r="J40" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" s="0" t="n"/>
+    </row>
+    <row r="41" s="1">
+      <c r="B41" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="C41" s="0" t="inlineStr">
+        <is>
+          <t>任务300接取成功：临时包扎</t>
+        </is>
+      </c>
+      <c r="D41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="G41" s="0" t="n"/>
+      <c r="J41" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L41" s="0" t="n"/>
+    </row>
+    <row r="42" s="1">
+      <c r="B42" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="C42" s="0" t="inlineStr">
+        <is>
+          <t>任务300接取失败：临时包扎</t>
+        </is>
+      </c>
+      <c r="D42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F42" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="G42" s="0" t="n"/>
+      <c r="J42" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L42" s="0" t="n"/>
+    </row>
+    <row r="43" s="1">
+      <c r="B43" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_first_aid</t>
+        </is>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>任务300复述：临时包扎</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F43" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_first_aid</t>
+        </is>
+      </c>
+      <c r="G43" s="0" t="n"/>
+      <c r="J43" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L43" s="0" t="n"/>
+    </row>
+    <row r="44" s="1">
+      <c r="B44" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_entry</t>
+        </is>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>任务300交付入口：临时包扎</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F44" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_entry</t>
+        </is>
+      </c>
+      <c r="G44" s="0" t="n"/>
+      <c r="J44" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L44" s="0" t="n"/>
+    </row>
+    <row r="45" s="1">
+      <c r="B45" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>任务300交付成功：临时包扎</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F45" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="G45" s="0" t="n"/>
+      <c r="J45" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L45" s="0" t="n"/>
+    </row>
+    <row r="46" s="1">
+      <c r="B46" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>任务300交付失败：临时包扎</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="G46" s="0" t="n"/>
+      <c r="J46" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L46" s="0" t="n"/>
+    </row>
+    <row r="47" s="1">
+      <c r="B47" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit</t>
+        </is>
+      </c>
+      <c r="C47" s="0" t="inlineStr">
+        <is>
+          <t>任务301接取入口：清理退路</t>
+        </is>
+      </c>
+      <c r="D47" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F47" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit</t>
+        </is>
+      </c>
+      <c r="G47" s="0" t="n"/>
+      <c r="J47" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L47" s="0" t="n"/>
+    </row>
+    <row r="48" s="1">
+      <c r="B48" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_ok</t>
+        </is>
+      </c>
+      <c r="C48" s="0" t="inlineStr">
+        <is>
+          <t>任务301接取成功：清理退路</t>
+        </is>
+      </c>
+      <c r="D48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_ok</t>
+        </is>
+      </c>
+      <c r="G48" s="0" t="n"/>
+      <c r="J48" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L48" s="0" t="n"/>
+    </row>
+    <row r="49" s="1">
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_fail</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>任务301接取失败：清理退路</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F49" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_fail</t>
+        </is>
+      </c>
+      <c r="G49" s="0" t="n"/>
+      <c r="J49" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L49" s="0" t="n"/>
+    </row>
+    <row r="50" s="1">
+      <c r="B50" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_clear_exit</t>
+        </is>
+      </c>
+      <c r="C50" s="0" t="inlineStr">
+        <is>
+          <t>任务301复述：清理退路</t>
+        </is>
+      </c>
+      <c r="D50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F50" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_clear_exit</t>
+        </is>
+      </c>
+      <c r="G50" s="0" t="n"/>
+      <c r="J50" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L50" s="0" t="n"/>
+    </row>
+    <row r="51" s="1">
+      <c r="B51" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher</t>
+        </is>
+      </c>
+      <c r="C51" s="0" t="inlineStr">
+        <is>
+          <t>任务302接取入口：简易担架</t>
+        </is>
+      </c>
+      <c r="D51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F51" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher</t>
+        </is>
+      </c>
+      <c r="G51" s="0" t="n"/>
+      <c r="J51" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L51" s="0" t="n"/>
+    </row>
+    <row r="52" s="1">
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>任务302接取成功：简易担架</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F52" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="G52" s="0" t="n"/>
+      <c r="J52" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L52" s="0" t="n"/>
+    </row>
+    <row r="53" s="1">
+      <c r="B53" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="C53" s="0" t="inlineStr">
+        <is>
+          <t>任务302接取失败：简易担架</t>
+        </is>
+      </c>
+      <c r="D53" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="G53" s="0" t="n"/>
+      <c r="J53" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L53" s="0" t="n"/>
+    </row>
+    <row r="54" s="1">
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_stretcher</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>任务302复述：简易担架</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F54" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_stretcher</t>
+        </is>
+      </c>
+      <c r="G54" s="0" t="n"/>
+      <c r="J54" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L54" s="0" t="n"/>
+    </row>
+    <row r="55" s="1">
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_entry</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>任务302交付入口：简易担架</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F55" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_entry</t>
+        </is>
+      </c>
+      <c r="G55" s="0" t="n"/>
+      <c r="J55" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L55" s="0" t="n"/>
+    </row>
+    <row r="56" s="1">
+      <c r="B56" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="C56" s="0" t="inlineStr">
+        <is>
+          <t>任务302交付成功：卡莱尔苏醒</t>
+        </is>
+      </c>
+      <c r="D56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F56" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="G56" s="0" t="n"/>
+      <c r="J56" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L56" s="0" t="n"/>
+    </row>
+    <row r="57" s="1">
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>任务302交付失败：简易担架</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F57" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="G57" s="0" t="n"/>
+      <c r="J57" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L57" s="0" t="n"/>
+    </row>
+    <row r="58" s="1">
+      <c r="B58" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_first_talk</t>
+        </is>
+      </c>
+      <c r="C58" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔苏醒后的首次对话</t>
+        </is>
+      </c>
+      <c r="D58" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E58" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_first_talk</t>
+        </is>
+      </c>
+      <c r="G58" s="0" t="n"/>
+      <c r="H58" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,302,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J58" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L58" s="0" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="59" s="1">
+      <c r="B59" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_entry</t>
+        </is>
+      </c>
+      <c r="C59" s="0" t="inlineStr">
+        <is>
+          <t>卡莱尔苏醒后的普通交互入口</t>
+        </is>
+      </c>
+      <c r="D59" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E59" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F59" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_entry</t>
+        </is>
+      </c>
+      <c r="G59" s="0" t="n"/>
+      <c r="J59" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L59" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -2136,7 +2872,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="2" max="2"/>
@@ -2330,7 +3066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" s="1">
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
@@ -2346,6 +3082,83 @@
       </c>
       <c r="E7" s="0" t="n">
         <v>3</v>
+      </c>
+    </row>
+    <row r="8" s="1">
+      <c r="B8" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>game_init_luca_injured</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_entry</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" s="1">
+      <c r="B9" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>game_init_carlisle_unconscious</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_unconscious_entry</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" s="1">
+      <c r="B10" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>game_init_carlisle_awake</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_first_talk</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,302,0,0,0,0,0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" s="1">
+      <c r="B11" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>game_init_carlisle_awake</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_awake_entry</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2374,7 +3187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -2943,7 +3756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" s="1">
       <c r="B16" s="0" t="n">
         <v>17</v>
       </c>
@@ -2973,6 +3786,611 @@
       </c>
       <c r="I16" s="0" t="inlineStr"/>
       <c r="K16" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1">
+      <c r="B17" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D17" s="0" t="n"/>
+      <c r="E17" s="0" t="n"/>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>检查他的伤势。</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,100,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" s="1">
+      <c r="B18" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D18" s="0" t="n"/>
+      <c r="E18" s="0" t="n"/>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>AcceptSuccess</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="n"/>
+      <c r="K18" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1">
+      <c r="B19" s="0" t="n">
+        <v>102</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D19" s="0" t="n"/>
+      <c r="E19" s="0" t="n"/>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>AcceptFail</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="n"/>
+      <c r="K19" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1">
+      <c r="B20" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>300_s1</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="n"/>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_first_aid</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>我该怎么稳定他的伤势？</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" s="1">
+      <c r="B21" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D21" s="0" t="n"/>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_entry</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>给他做临时包扎。</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" s="1">
+      <c r="B22" s="0" t="n">
+        <v>105</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" s="0" t="n"/>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
+      <c r="F22" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="n"/>
+      <c r="K22" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" s="1">
+      <c r="B23" s="0" t="n">
+        <v>106</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D23" s="0" t="n"/>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
+      <c r="F23" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
+        <is>
+          <t>FulfillFail</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="I23" s="0" t="n"/>
+      <c r="K23" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" s="1">
+      <c r="B24" s="0" t="n">
+        <v>110</v>
+      </c>
+      <c r="C24" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="D24" s="0" t="n"/>
+      <c r="E24" s="0" t="n"/>
+      <c r="F24" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit</t>
+        </is>
+      </c>
+      <c r="I24" s="0" t="inlineStr">
+        <is>
+          <t>先把附近的怪物清掉。</t>
+        </is>
+      </c>
+      <c r="J24" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,300,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" s="1">
+      <c r="B25" s="0" t="n">
+        <v>111</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="D25" s="0" t="n"/>
+      <c r="E25" s="0" t="n"/>
+      <c r="F25" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>AcceptSuccess</t>
+        </is>
+      </c>
+      <c r="H25" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_ok</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="n"/>
+      <c r="K25" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" s="1">
+      <c r="B26" s="0" t="n">
+        <v>112</v>
+      </c>
+      <c r="C26" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="D26" s="0" t="n"/>
+      <c r="E26" s="0" t="n"/>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G26" s="0" t="inlineStr">
+        <is>
+          <t>AcceptFail</t>
+        </is>
+      </c>
+      <c r="H26" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_fail</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="n"/>
+      <c r="K26" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" s="1">
+      <c r="B27" s="0" t="n">
+        <v>113</v>
+      </c>
+      <c r="C27" s="0" t="n">
+        <v>301</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>301_s1</t>
+        </is>
+      </c>
+      <c r="E27" s="0" t="n"/>
+      <c r="F27" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G27" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H27" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_clear_exit</t>
+        </is>
+      </c>
+      <c r="I27" s="0" t="inlineStr">
+        <is>
+          <t>退路还不安全。</t>
+        </is>
+      </c>
+      <c r="K27" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" s="1">
+      <c r="B28" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="C28" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D28" s="0" t="n"/>
+      <c r="E28" s="0" t="n"/>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>Accept</t>
+        </is>
+      </c>
+      <c r="H28" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher</t>
+        </is>
+      </c>
+      <c r="I28" s="0" t="inlineStr">
+        <is>
+          <t>做个能带他离开的东西。</t>
+        </is>
+      </c>
+      <c r="J28" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,301,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="K28" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" s="1">
+      <c r="B29" s="0" t="n">
+        <v>121</v>
+      </c>
+      <c r="C29" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D29" s="0" t="n"/>
+      <c r="E29" s="0" t="n"/>
+      <c r="F29" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>AcceptSuccess</t>
+        </is>
+      </c>
+      <c r="H29" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="n"/>
+      <c r="K29" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" s="1">
+      <c r="B30" s="0" t="n">
+        <v>122</v>
+      </c>
+      <c r="C30" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D30" s="0" t="n"/>
+      <c r="E30" s="0" t="n"/>
+      <c r="F30" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>AcceptFail</t>
+        </is>
+      </c>
+      <c r="H30" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="n"/>
+      <c r="K30" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" s="1">
+      <c r="B31" s="0" t="n">
+        <v>123</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D31" s="0" t="inlineStr">
+        <is>
+          <t>302_s1</t>
+        </is>
+      </c>
+      <c r="E31" s="0" t="n"/>
+      <c r="F31" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H31" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_stretcher</t>
+        </is>
+      </c>
+      <c r="I31" s="0" t="inlineStr">
+        <is>
+          <t>还需要能固定他的材料。</t>
+        </is>
+      </c>
+      <c r="K31" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" s="1">
+      <c r="B32" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D32" s="0" t="n"/>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>302_s2_Main</t>
+        </is>
+      </c>
+      <c r="F32" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_entry</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>把简易担架固定好。</t>
+        </is>
+      </c>
+      <c r="K32" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" s="1">
+      <c r="B33" s="0" t="n">
+        <v>125</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D33" s="0" t="n"/>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>302_s2_Main</t>
+        </is>
+      </c>
+      <c r="F33" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G33" s="0" t="inlineStr">
+        <is>
+          <t>FulfillSuccess</t>
+        </is>
+      </c>
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="n"/>
+      <c r="K33" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="1">
+      <c r="B34" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D34" s="0" t="n"/>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>302_s2_Main</t>
+        </is>
+      </c>
+      <c r="F34" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G34" s="0" t="inlineStr">
+        <is>
+          <t>FulfillFail</t>
+        </is>
+      </c>
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="n"/>
+      <c r="K34" s="0" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="40.625" customWidth="1" style="1" min="2" max="2"/>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>base_fight</t>
+          <t>homestead_01_fight</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -2858,6 +2858,45 @@
       </c>
       <c r="L59" s="0" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>transition_a_bandits_north</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>????A??????????????????????</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" s="0" t="inlineStr">
+        <is>
+          <t>transition_a_bandits_north</t>
+        </is>
+      </c>
+      <c r="G60" s="0" t="inlineStr">
+        <is>
+          <t>test_link_a</t>
+        </is>
+      </c>
+      <c r="H60" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,302,0,0,0,0,0</t>
+        </is>
+      </c>
+      <c r="J60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="L60" s="0" t="n">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -3558,6 +3597,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="0" t="n">
         <v>11</v>
@@ -3820,7 +3860,7 @@
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>TaskFinish,100,0,0,0,0,0</t>
+          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
         </is>
       </c>
       <c r="K17" s="0" t="n">

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dialog_meta_info" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="npc_dialog_info" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="quest_interact_dialog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="dialog_meta_info" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="npc_dialog_info" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="quest_interact_dialog" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -2899,6 +2899,40 @@
         <v>120</v>
       </c>
     </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>forest_reed_pillar_01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>?????????</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>forest_reed_pillar_01</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>forest_01</t>
+        </is>
+      </c>
+      <c r="J61" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -3226,7 +3260,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -3457,269 +3491,275 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="D5" s="0" t="inlineStr">
-        <is>
-          <t>200_s1</t>
-        </is>
-      </c>
-      <c r="E5" s="0" t="inlineStr"/>
-      <c r="F5" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G5" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H5" s="0" t="inlineStr">
-        <is>
-          <t>homestead_remind_herb</t>
-        </is>
-      </c>
-      <c r="I5" s="0" t="inlineStr">
-        <is>
-          <t>我还该做什么？</t>
-        </is>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="D6" s="0" t="inlineStr"/>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>200_s2_Main</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D6" s="0" t="n"/>
+      <c r="E6" s="0" t="n"/>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>home_elder</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Fulfill</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_herb_entry</t>
+          <t>carlisle_accept_first_aid</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>这些草药给你。</t>
+          <t>检查他的伤势。</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
         </is>
       </c>
       <c r="K6" s="0" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="D7" s="0" t="inlineStr"/>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>200_s2_Main</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D7" s="0" t="n"/>
+      <c r="E7" s="0" t="n"/>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>home_elder</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>FulfillSuccess</t>
+          <t>AcceptSuccess</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_herb_ok</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="inlineStr"/>
+          <t>carlisle_accept_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="n"/>
       <c r="K7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="n">
-        <v>4</v>
+        <v>102</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>200</v>
-      </c>
-      <c r="D8" s="0" t="inlineStr"/>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>200_s2_Main</t>
-        </is>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="D8" s="0" t="n"/>
+      <c r="E8" s="0" t="n"/>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>home_elder</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>FulfillFail</t>
+          <t>AcceptFail</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_herb_fail</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="inlineStr"/>
+          <t>carlisle_accept_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="n"/>
       <c r="K8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="B9" s="0" t="n">
+        <v>103</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>300_s1</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="n"/>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_remind_first_aid</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>我该怎么稳定他的伤势？</t>
+        </is>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
     <row r="10">
       <c r="B10" s="0" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D10" s="0" t="inlineStr"/>
-      <c r="E10" s="0" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="D10" s="0" t="n"/>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
       <c r="F10" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>Accept</t>
+          <t>Fulfill</t>
         </is>
       </c>
       <c r="H10" s="0" t="inlineStr">
         <is>
-          <t>homestead_accept_wood</t>
+          <t>carlisle_submit_first_aid_entry</t>
         </is>
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>关于采集木材……</t>
+          <t>给他做临时包扎。</t>
         </is>
       </c>
       <c r="K10" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
-        <v>12</v>
+        <v>105</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D11" s="0" t="inlineStr"/>
-      <c r="E11" s="0" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="D11" s="0" t="n"/>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
       <c r="F11" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
+          <t>FulfillSuccess</t>
         </is>
       </c>
       <c r="H11" s="0" t="inlineStr">
         <is>
-          <t>homestead_accept_wood_ok</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="inlineStr"/>
+          <t>carlisle_submit_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="I11" s="0" t="n"/>
       <c r="K11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
-        <v>13</v>
+        <v>106</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D12" s="0" t="inlineStr"/>
-      <c r="E12" s="0" t="inlineStr"/>
+        <v>300</v>
+      </c>
+      <c r="D12" s="0" t="n"/>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
       <c r="F12" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>AcceptFail</t>
+          <t>FulfillFail</t>
         </is>
       </c>
       <c r="H12" s="0" t="inlineStr">
         <is>
-          <t>homestead_accept_wood_fail</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="inlineStr"/>
+          <t>carlisle_submit_first_aid_fail</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="n"/>
       <c r="K12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D13" s="0" t="inlineStr">
-        <is>
-          <t>201_s1</t>
-        </is>
-      </c>
-      <c r="E13" s="0" t="inlineStr"/>
+        <v>301</v>
+      </c>
+      <c r="D13" s="0" t="n"/>
+      <c r="E13" s="0" t="n"/>
       <c r="F13" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>Remind</t>
+          <t>Accept</t>
         </is>
       </c>
       <c r="H13" s="0" t="inlineStr">
         <is>
-          <t>homestead_remind_wood</t>
+          <t>carlisle_accept_clear_exit</t>
         </is>
       </c>
       <c r="I13" s="0" t="inlineStr">
         <is>
-          <t>我还该做什么？</t>
+          <t>先把附近的怪物清掉。</t>
+        </is>
+      </c>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,300,0,0,0,0,0</t>
         </is>
       </c>
       <c r="K13" s="0" t="n">
@@ -3728,113 +3768,105 @@
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D14" s="0" t="inlineStr"/>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>201_s2_Main</t>
-        </is>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="D14" s="0" t="n"/>
+      <c r="E14" s="0" t="n"/>
       <c r="F14" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>Fulfill</t>
+          <t>AcceptSuccess</t>
         </is>
       </c>
       <c r="H14" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_wood_entry</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="inlineStr">
-        <is>
-          <t>这些木材给你。</t>
-        </is>
-      </c>
+          <t>carlisle_accept_clear_exit_ok</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="n"/>
       <c r="K14" s="0" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
-        <v>16</v>
+        <v>112</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D15" s="0" t="inlineStr"/>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>201_s2_Main</t>
-        </is>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="D15" s="0" t="n"/>
+      <c r="E15" s="0" t="n"/>
       <c r="F15" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>FulfillSuccess</t>
+          <t>AcceptFail</t>
         </is>
       </c>
       <c r="H15" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_wood_ok</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="inlineStr"/>
+          <t>carlisle_accept_clear_exit_fail</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="n"/>
       <c r="K15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" s="1">
       <c r="B16" s="0" t="n">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="D16" s="0" t="inlineStr"/>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>201_s2_Main</t>
-        </is>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>301_s1</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="n"/>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>home_merchant</t>
+          <t>carlisle</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>FulfillFail</t>
+          <t>Remind</t>
         </is>
       </c>
       <c r="H16" s="0" t="inlineStr">
         <is>
-          <t>homestead_submit_wood_fail</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr"/>
+          <t>carlisle_remind_clear_exit</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr">
+        <is>
+          <t>退路还不安全。</t>
+        </is>
+      </c>
       <c r="K16" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" s="1">
       <c r="B17" s="0" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D17" s="0" t="n"/>
       <c r="E17" s="0" t="n"/>
@@ -3850,17 +3882,17 @@
       </c>
       <c r="H17" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid</t>
+          <t>carlisle_accept_stretcher</t>
         </is>
       </c>
       <c r="I17" s="0" t="inlineStr">
         <is>
-          <t>检查他的伤势。</t>
+          <t>做个能带他离开的东西。</t>
         </is>
       </c>
       <c r="J17" s="0" t="inlineStr">
         <is>
-          <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
+          <t>TaskFinish,301,0,0,0,0,0</t>
         </is>
       </c>
       <c r="K17" s="0" t="n">
@@ -3869,10 +3901,10 @@
     </row>
     <row r="18" s="1">
       <c r="B18" s="0" t="n">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D18" s="0" t="n"/>
       <c r="E18" s="0" t="n"/>
@@ -3888,7 +3920,7 @@
       </c>
       <c r="H18" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid_ok</t>
+          <t>carlisle_accept_stretcher_ok</t>
         </is>
       </c>
       <c r="I18" s="0" t="n"/>
@@ -3898,10 +3930,10 @@
     </row>
     <row r="19" s="1">
       <c r="B19" s="0" t="n">
-        <v>102</v>
+        <v>122</v>
       </c>
       <c r="C19" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D19" s="0" t="n"/>
       <c r="E19" s="0" t="n"/>
@@ -3917,7 +3949,7 @@
       </c>
       <c r="H19" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid_fail</t>
+          <t>carlisle_accept_stretcher_fail</t>
         </is>
       </c>
       <c r="I19" s="0" t="n"/>
@@ -3927,14 +3959,14 @@
     </row>
     <row r="20" s="1">
       <c r="B20" s="0" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="C20" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D20" s="0" t="inlineStr">
         <is>
-          <t>300_s1</t>
+          <t>302_s1</t>
         </is>
       </c>
       <c r="E20" s="0" t="n"/>
@@ -3950,12 +3982,12 @@
       </c>
       <c r="H20" s="0" t="inlineStr">
         <is>
-          <t>carlisle_remind_first_aid</t>
+          <t>carlisle_remind_stretcher</t>
         </is>
       </c>
       <c r="I20" s="0" t="inlineStr">
         <is>
-          <t>我该怎么稳定他的伤势？</t>
+          <t>还需要能固定他的材料。</t>
         </is>
       </c>
       <c r="K20" s="0" t="n">
@@ -3964,15 +3996,15 @@
     </row>
     <row r="21" s="1">
       <c r="B21" s="0" t="n">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C21" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D21" s="0" t="n"/>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="F21" s="0" t="inlineStr">
@@ -3987,12 +4019,12 @@
       </c>
       <c r="H21" s="0" t="inlineStr">
         <is>
-          <t>carlisle_submit_first_aid_entry</t>
+          <t>carlisle_submit_stretcher_entry</t>
         </is>
       </c>
       <c r="I21" s="0" t="inlineStr">
         <is>
-          <t>给他做临时包扎。</t>
+          <t>把简易担架固定好。</t>
         </is>
       </c>
       <c r="K21" s="0" t="n">
@@ -4001,15 +4033,15 @@
     </row>
     <row r="22" s="1">
       <c r="B22" s="0" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="C22" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D22" s="0" t="n"/>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="F22" s="0" t="inlineStr">
@@ -4024,7 +4056,7 @@
       </c>
       <c r="H22" s="0" t="inlineStr">
         <is>
-          <t>carlisle_submit_first_aid_ok</t>
+          <t>carlisle_submit_stretcher_ok</t>
         </is>
       </c>
       <c r="I22" s="0" t="n"/>
@@ -4034,15 +4066,15 @@
     </row>
     <row r="23" s="1">
       <c r="B23" s="0" t="n">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C23" s="0" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D23" s="0" t="n"/>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
+          <t>302_s2_Main</t>
         </is>
       </c>
       <c r="F23" s="0" t="inlineStr">
@@ -4057,7 +4089,7 @@
       </c>
       <c r="H23" s="0" t="inlineStr">
         <is>
-          <t>carlisle_submit_first_aid_fail</t>
+          <t>carlisle_submit_stretcher_fail</t>
         </is>
       </c>
       <c r="I23" s="0" t="n"/>
@@ -4067,169 +4099,153 @@
     </row>
     <row r="24" s="1">
       <c r="B24" s="0" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C24" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D24" s="0" t="n"/>
-      <c r="E24" s="0" t="n"/>
+        <v>201</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>201_s1_Main</t>
+        </is>
+      </c>
       <c r="F24" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G24" s="0" t="inlineStr">
         <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="H24" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit</t>
+          <t>Fulfill</t>
         </is>
       </c>
       <c r="I24" s="0" t="inlineStr">
         <is>
-          <t>先把附近的怪物清掉。</t>
-        </is>
-      </c>
-      <c r="J24" s="0" t="inlineStr">
-        <is>
-          <t>TaskFinish,300,0,0,0,0,0</t>
+          <t>到火堆边谈谈。</t>
         </is>
       </c>
       <c r="K24" s="0" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" s="1">
       <c r="B25" s="0" t="n">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C25" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D25" s="0" t="n"/>
-      <c r="E25" s="0" t="n"/>
+        <v>202</v>
+      </c>
+      <c r="E25" s="0" t="inlineStr">
+        <is>
+          <t>202_s1_Main</t>
+        </is>
+      </c>
       <c r="F25" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G25" s="0" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
-        </is>
-      </c>
-      <c r="H25" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit_ok</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="n"/>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="I25" s="0" t="inlineStr">
+        <is>
+          <t>确认幸存者人数。</t>
+        </is>
+      </c>
       <c r="K25" s="0" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" s="1">
       <c r="B26" s="0" t="n">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C26" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D26" s="0" t="n"/>
-      <c r="E26" s="0" t="n"/>
+        <v>203</v>
+      </c>
+      <c r="D26" s="0" t="inlineStr">
+        <is>
+          <t>203_s1</t>
+        </is>
+      </c>
       <c r="F26" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>AcceptFail</t>
-        </is>
-      </c>
-      <c r="H26" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit_fail</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="n"/>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="I26" s="0" t="inlineStr">
+        <is>
+          <t>火堆还缺什么？</t>
+        </is>
+      </c>
       <c r="K26" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" s="1">
       <c r="B27" s="0" t="n">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C27" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D27" s="0" t="inlineStr">
-        <is>
-          <t>301_s1</t>
-        </is>
-      </c>
-      <c r="E27" s="0" t="n"/>
+        <v>203</v>
+      </c>
+      <c r="E27" s="0" t="inlineStr">
+        <is>
+          <t>203_s2_Main</t>
+        </is>
+      </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G27" s="0" t="inlineStr">
         <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H27" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_remind_clear_exit</t>
+          <t>Fulfill</t>
         </is>
       </c>
       <c r="I27" s="0" t="inlineStr">
         <is>
-          <t>退路还不安全。</t>
+          <t>把木料交给他。</t>
         </is>
       </c>
       <c r="K27" s="0" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28" s="1">
       <c r="B28" s="0" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C28" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D28" s="0" t="n"/>
-      <c r="E28" s="0" t="n"/>
+        <v>204</v>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
+        <is>
+          <t>204_s1</t>
+        </is>
+      </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="H28" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher</t>
+          <t>Remind</t>
         </is>
       </c>
       <c r="I28" s="0" t="inlineStr">
         <is>
-          <t>做个能带他离开的东西。</t>
-        </is>
-      </c>
-      <c r="J28" s="0" t="inlineStr">
-        <is>
-          <t>TaskFinish,301,0,0,0,0,0</t>
+          <t>灰露草棚要怎么处理？</t>
         </is>
       </c>
       <c r="K28" s="0" t="n">
@@ -4238,78 +4254,81 @@
     </row>
     <row r="29" s="1">
       <c r="B29" s="0" t="n">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="C29" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D29" s="0" t="n"/>
-      <c r="E29" s="0" t="n"/>
+        <v>204</v>
+      </c>
+      <c r="E29" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
       <c r="F29" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G29" s="0" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
-        </is>
-      </c>
-      <c r="H29" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher_ok</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="n"/>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="I29" s="0" t="inlineStr">
+        <is>
+          <t>把灰露草送过去。</t>
+        </is>
+      </c>
       <c r="K29" s="0" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" s="1">
       <c r="B30" s="0" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="C30" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D30" s="0" t="n"/>
-      <c r="E30" s="0" t="n"/>
+        <v>205</v>
+      </c>
+      <c r="E30" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
       <c r="F30" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G30" s="0" t="inlineStr">
         <is>
-          <t>AcceptFail</t>
-        </is>
-      </c>
-      <c r="H30" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher_fail</t>
-        </is>
-      </c>
-      <c r="I30" s="0" t="n"/>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="I30" s="0" t="inlineStr">
+        <is>
+          <t>确认临时住处已整理。</t>
+        </is>
+      </c>
       <c r="K30" s="0" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" s="1">
       <c r="B31" s="0" t="n">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C31" s="0" t="n">
-        <v>302</v>
+        <v>206</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
-          <t>302_s1</t>
-        </is>
-      </c>
-      <c r="E31" s="0" t="n"/>
+          <t>206_s1</t>
+        </is>
+      </c>
       <c r="F31" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G31" s="0" t="inlineStr">
@@ -4317,14 +4336,9 @@
           <t>Remind</t>
         </is>
       </c>
-      <c r="H31" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_remind_stretcher</t>
-        </is>
-      </c>
       <c r="I31" s="0" t="inlineStr">
         <is>
-          <t>还需要能固定他的材料。</t>
+          <t>村外的路标怎么补？</t>
         </is>
       </c>
       <c r="K31" s="0" t="n">
@@ -4333,20 +4347,19 @@
     </row>
     <row r="32" s="1">
       <c r="B32" s="0" t="n">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="C32" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D32" s="0" t="n"/>
+        <v>206</v>
+      </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>206_s2_Main</t>
         </is>
       </c>
       <c r="F32" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G32" s="0" t="inlineStr">
@@ -4354,14 +4367,9 @@
           <t>Fulfill</t>
         </is>
       </c>
-      <c r="H32" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_entry</t>
-        </is>
-      </c>
       <c r="I32" s="0" t="inlineStr">
         <is>
-          <t>把简易担架固定好。</t>
+          <t>把路标材料交给他。</t>
         </is>
       </c>
       <c r="K32" s="0" t="n">
@@ -4370,68 +4378,95 @@
     </row>
     <row r="33" s="1">
       <c r="B33" s="0" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C33" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D33" s="0" t="n"/>
+        <v>207</v>
+      </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>302_s2_Main</t>
+          <t>207_s1_Main</t>
         </is>
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G33" s="0" t="inlineStr">
         <is>
-          <t>FulfillSuccess</t>
-        </is>
-      </c>
-      <c r="H33" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_ok</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="n"/>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>开放村东通路。</t>
+        </is>
+      </c>
       <c r="K33" s="0" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="34" s="1">
       <c r="B34" s="0" t="n">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="C34" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D34" s="0" t="n"/>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>302_s2_Main</t>
+        <v>208</v>
+      </c>
+      <c r="D34" s="0" t="inlineStr">
+        <is>
+          <t>208_s1</t>
         </is>
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G34" s="0" t="inlineStr">
         <is>
-          <t>FulfillFail</t>
-        </is>
-      </c>
-      <c r="H34" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_fail</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="n"/>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>需要带回什么样本？</t>
+        </is>
+      </c>
       <c r="K34" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>208</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="F35" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>把雾线样本交给埃蒙。</t>
+        </is>
+      </c>
+      <c r="K35" s="0" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="40.625" customWidth="1" style="1" min="2" max="2"/>
@@ -2899,38 +2899,158 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
+    <row r="61" s="1">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>forest_reed_pillar_01</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>?????????</t>
         </is>
       </c>
-      <c r="D61" t="b">
-        <v>0</v>
-      </c>
-      <c r="E61" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr">
+      <c r="D61" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E61" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F61" s="0" t="inlineStr">
         <is>
           <t>forest_reed_pillar_01</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>forest_01</t>
         </is>
       </c>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="L61">
-        <v>0</v>
+      <c r="J61" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L61" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" s="1">
+      <c r="B62" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_remind</t>
+        </is>
+      </c>
+      <c r="C62" s="0" t="inlineStr">
+        <is>
+          <t>任务211提示</t>
+        </is>
+      </c>
+      <c r="D62" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E62" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F62" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_remind</t>
+        </is>
+      </c>
+      <c r="G62" s="0" t="n"/>
+      <c r="J62" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L62" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="63" s="1">
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_fulfill</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>任务211交付</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F63" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_fulfill</t>
+        </is>
+      </c>
+      <c r="G63" s="0" t="n"/>
+      <c r="J63" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L63" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" s="1">
+      <c r="B64" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_remind</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>任务212提示</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E64" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F64" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_remind</t>
+        </is>
+      </c>
+      <c r="G64" s="0" t="n"/>
+      <c r="J64" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L64" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" s="1">
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_fulfill</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>任务212交付</t>
+        </is>
+      </c>
+      <c r="D65" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E65" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F65" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_fulfill</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="n"/>
+      <c r="J65" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L65" s="0" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3260,7 +3380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData>
     <row r="1">
@@ -4438,7 +4558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" s="1">
       <c r="B35" s="0" t="n">
         <v>138</v>
       </c>
@@ -4466,6 +4586,153 @@
         </is>
       </c>
       <c r="K35" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" s="1">
+      <c r="B36" s="0" t="n">
+        <v>139</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="D36" s="0" t="inlineStr">
+        <is>
+          <t>211_s1</t>
+        </is>
+      </c>
+      <c r="E36" s="0" t="n"/>
+      <c r="F36" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G36" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_remind</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>北路的花露有什么特征？</t>
+        </is>
+      </c>
+      <c r="K36" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" s="1">
+      <c r="B37" s="0" t="n">
+        <v>140</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>211</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="F37" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G37" s="0" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_211_fulfill</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>交出两份森林花露。</t>
+        </is>
+      </c>
+      <c r="K37" s="0" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" s="1">
+      <c r="B38" s="0" t="n">
+        <v>141</v>
+      </c>
+      <c r="C38" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="D38" s="0" t="inlineStr">
+        <is>
+          <t>212_s1</t>
+        </is>
+      </c>
+      <c r="E38" s="0" t="n"/>
+      <c r="F38" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G38" s="0" t="inlineStr">
+        <is>
+          <t>Remind</t>
+        </is>
+      </c>
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_remind</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>森林之心究竟是什么？</t>
+        </is>
+      </c>
+      <c r="K38" s="0" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" s="1">
+      <c r="B39" s="0" t="n">
+        <v>142</v>
+      </c>
+      <c r="C39" s="0" t="n">
+        <v>212</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="F39" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G39" s="0" t="inlineStr">
+        <is>
+          <t>Fulfill</t>
+        </is>
+      </c>
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>forest_quest_212_fulfill</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>汇报森林之心的反应。</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n"/>
+      <c r="K39" s="0" t="n">
         <v>20</v>
       </c>
     </row>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -3,23 +3,25 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="dialog_meta_info" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="npc_dialog_info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="quest_interact_dialog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="quest_accept_dialog" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="quest_remind_dialog" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="quest_objective_dialog" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="2">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -29,344 +31,21 @@
     </font>
     <font>
       <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <family val="3"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -374,251 +53,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -631,56 +68,8 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -998,6 +387,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1007,12 +397,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col width="40.625" customWidth="1" style="1" min="2" max="2"/>
-    <col width="26.25" customWidth="1" style="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" style="1" min="4" max="7"/>
+    <col width="28.625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="32.625" customWidth="1" style="1" min="3" max="3"/>
+    <col width="13.5" customWidth="1" style="1" min="4" max="5"/>
+    <col width="28.625" customWidth="1" style="1" min="6" max="6"/>
+    <col width="13.5" customWidth="1" style="1" min="7" max="7"/>
     <col width="13.875" customWidth="1" style="1" min="8" max="8"/>
     <col width="13.375" customWidth="1" style="1" min="9" max="9"/>
     <col width="10.5" customWidth="1" style="1" min="10" max="10"/>
@@ -2124,7 +1516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" s="1">
+    <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
           <t>forest_gujou_reunion</t>
@@ -2158,7 +1550,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="36" s="1">
+    <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
           <t>game_init_lilith_wakeup_tutorial</t>
@@ -2192,7 +1584,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="37" s="1">
+    <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
           <t>game_init_after_first_monsters</t>
@@ -2231,7 +1623,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="38" s="1">
+    <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
           <t>carlisle_unconscious_entry</t>
@@ -2261,7 +1653,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="39" s="1">
+    <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
           <t>carlisle_unconscious_first_check</t>
@@ -2291,7 +1683,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" s="1">
+    <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_first_aid</t>
@@ -2319,7 +1711,7 @@
       </c>
       <c r="L40" s="0" t="n"/>
     </row>
-    <row r="41" s="1">
+    <row r="41">
       <c r="B41" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_first_aid_ok</t>
@@ -2347,7 +1739,7 @@
       </c>
       <c r="L41" s="0" t="n"/>
     </row>
-    <row r="42" s="1">
+    <row r="42">
       <c r="B42" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_first_aid_fail</t>
@@ -2375,7 +1767,7 @@
       </c>
       <c r="L42" s="0" t="n"/>
     </row>
-    <row r="43" s="1">
+    <row r="43">
       <c r="B43" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_first_aid</t>
@@ -2403,7 +1795,7 @@
       </c>
       <c r="L43" s="0" t="n"/>
     </row>
-    <row r="44" s="1">
+    <row r="44">
       <c r="B44" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_first_aid_entry</t>
@@ -2431,7 +1823,7 @@
       </c>
       <c r="L44" s="0" t="n"/>
     </row>
-    <row r="45" s="1">
+    <row r="45">
       <c r="B45" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_first_aid_ok</t>
@@ -2459,7 +1851,7 @@
       </c>
       <c r="L45" s="0" t="n"/>
     </row>
-    <row r="46" s="1">
+    <row r="46">
       <c r="B46" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_first_aid_fail</t>
@@ -2487,7 +1879,7 @@
       </c>
       <c r="L46" s="0" t="n"/>
     </row>
-    <row r="47" s="1">
+    <row r="47">
       <c r="B47" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_clear_exit</t>
@@ -2515,7 +1907,7 @@
       </c>
       <c r="L47" s="0" t="n"/>
     </row>
-    <row r="48" s="1">
+    <row r="48">
       <c r="B48" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_clear_exit_ok</t>
@@ -2543,7 +1935,7 @@
       </c>
       <c r="L48" s="0" t="n"/>
     </row>
-    <row r="49" s="1">
+    <row r="49">
       <c r="B49" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_clear_exit_fail</t>
@@ -2571,7 +1963,7 @@
       </c>
       <c r="L49" s="0" t="n"/>
     </row>
-    <row r="50" s="1">
+    <row r="50">
       <c r="B50" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_clear_exit</t>
@@ -2599,7 +1991,7 @@
       </c>
       <c r="L50" s="0" t="n"/>
     </row>
-    <row r="51" s="1">
+    <row r="51">
       <c r="B51" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_stretcher</t>
@@ -2627,7 +2019,7 @@
       </c>
       <c r="L51" s="0" t="n"/>
     </row>
-    <row r="52" s="1">
+    <row r="52">
       <c r="B52" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_stretcher_ok</t>
@@ -2655,7 +2047,7 @@
       </c>
       <c r="L52" s="0" t="n"/>
     </row>
-    <row r="53" s="1">
+    <row r="53">
       <c r="B53" s="0" t="inlineStr">
         <is>
           <t>carlisle_accept_stretcher_fail</t>
@@ -2683,7 +2075,7 @@
       </c>
       <c r="L53" s="0" t="n"/>
     </row>
-    <row r="54" s="1">
+    <row r="54">
       <c r="B54" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_stretcher</t>
@@ -2711,7 +2103,7 @@
       </c>
       <c r="L54" s="0" t="n"/>
     </row>
-    <row r="55" s="1">
+    <row r="55">
       <c r="B55" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_stretcher_entry</t>
@@ -2739,7 +2131,7 @@
       </c>
       <c r="L55" s="0" t="n"/>
     </row>
-    <row r="56" s="1">
+    <row r="56">
       <c r="B56" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_stretcher_ok</t>
@@ -2767,7 +2159,7 @@
       </c>
       <c r="L56" s="0" t="n"/>
     </row>
-    <row r="57" s="1">
+    <row r="57">
       <c r="B57" s="0" t="inlineStr">
         <is>
           <t>carlisle_submit_stretcher_fail</t>
@@ -2795,7 +2187,7 @@
       </c>
       <c r="L57" s="0" t="n"/>
     </row>
-    <row r="58" s="1">
+    <row r="58">
       <c r="B58" s="0" t="inlineStr">
         <is>
           <t>carlisle_awake_first_talk</t>
@@ -2830,7 +2222,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" s="1">
+    <row r="59">
       <c r="B59" s="0" t="inlineStr">
         <is>
           <t>carlisle_awake_entry</t>
@@ -2899,7 +2291,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" s="1">
+    <row r="61">
       <c r="B61" s="0" t="inlineStr">
         <is>
           <t>forest_reed_pillar_01</t>
@@ -2933,7 +2325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" s="1">
+    <row r="62">
       <c r="B62" s="0" t="inlineStr">
         <is>
           <t>forest_quest_211_remind</t>
@@ -2963,7 +2355,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="63" s="1">
+    <row r="63">
       <c r="B63" s="0" t="inlineStr">
         <is>
           <t>forest_quest_211_fulfill</t>
@@ -2993,7 +2385,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64" s="1">
+    <row r="64">
       <c r="B64" s="0" t="inlineStr">
         <is>
           <t>forest_quest_212_remind</t>
@@ -3023,7 +2415,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" s="1">
+    <row r="65">
       <c r="B65" s="0" t="inlineStr">
         <is>
           <t>forest_quest_212_fulfill</t>
@@ -3051,6 +2443,186 @@
       </c>
       <c r="L65" s="0" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>任务213接取入口</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F66" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="n"/>
+      <c r="J66" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L66" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_ok</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>任务213接取成功并解锁梦境</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_ok</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="n"/>
+      <c r="J67" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L67" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_fail</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>任务213接取失败</t>
+        </is>
+      </c>
+      <c r="D68" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E68" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F68" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_fail</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="n"/>
+      <c r="J68" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L68" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_remind</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>任务213入梦阶段复述</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F69" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_remind</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="n"/>
+      <c r="J69" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L69" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_after</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>任务213梦醒后回报入口</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E70" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F70" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_after</t>
+        </is>
+      </c>
+      <c r="G70" s="0" t="n"/>
+      <c r="J70" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L70" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_complete</t>
+        </is>
+      </c>
+      <c r="C71" s="0" t="inlineStr">
+        <is>
+          <t>任务213完成确认并关闭入口</t>
+        </is>
+      </c>
+      <c r="D71" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E71" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_complete</t>
+        </is>
+      </c>
+      <c r="G71" s="0" t="n"/>
+      <c r="J71" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L71" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3066,7 +2638,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="6"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="2" max="2"/>
     <col width="27.75" customWidth="1" style="1" min="3" max="3"/>
@@ -3259,7 +2831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" s="1">
+    <row r="7">
       <c r="B7" s="0" t="n">
         <v>3</v>
       </c>
@@ -3277,7 +2849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" s="1">
+    <row r="8">
       <c r="B8" s="0" t="n">
         <v>100</v>
       </c>
@@ -3295,7 +2867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" s="1">
+    <row r="9">
       <c r="B9" s="0" t="n">
         <v>101</v>
       </c>
@@ -3313,7 +2885,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" s="1">
+    <row r="10">
       <c r="B10" s="0" t="n">
         <v>102</v>
       </c>
@@ -3336,7 +2908,7 @@
         </is>
       </c>
     </row>
-    <row r="11" s="1">
+    <row r="11">
       <c r="B11" s="0" t="n">
         <v>103</v>
       </c>
@@ -3380,8 +2952,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="inlineStr">
@@ -3401,42 +2973,37 @@
       </c>
       <c r="D1" s="0" t="inlineStr">
         <is>
-          <t>step_id</t>
+          <t>character_key</t>
         </is>
       </c>
       <c r="E1" s="0" t="inlineStr">
         <is>
-          <t>obj_id</t>
+          <t>entry_dialog_id</t>
         </is>
       </c>
       <c r="F1" s="0" t="inlineStr">
         <is>
-          <t>character_key</t>
+          <t>option_text</t>
         </is>
       </c>
       <c r="G1" s="0" t="inlineStr">
         <is>
-          <t>dialog_role</t>
+          <t>priority</t>
         </is>
       </c>
       <c r="H1" s="0" t="inlineStr">
         <is>
-          <t>dialog_id</t>
+          <t>success_dialog_id</t>
         </is>
       </c>
       <c r="I1" s="0" t="inlineStr">
         <is>
-          <t>option_text</t>
+          <t>fail_dialog_id</t>
         </is>
       </c>
       <c r="J1" s="0" t="inlineStr">
         <is>
-          <t>show_cond</t>
-        </is>
-      </c>
-      <c r="K1" s="0" t="inlineStr">
-        <is>
-          <t>priority</t>
+          <t>open_cond</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3040,7 @@
       </c>
       <c r="G2" s="0" t="inlineStr">
         <is>
-          <t>EQuestDialogRole</t>
+          <t>int</t>
         </is>
       </c>
       <c r="H2" s="0" t="inlineStr">
@@ -3489,11 +3056,6 @@
       <c r="J2" s="0" t="inlineStr">
         <is>
           <t>(list#sep=;),CommonCheckCond</t>
-        </is>
-      </c>
-      <c r="K2" s="0" t="inlineStr">
-        <is>
-          <t>int</t>
         </is>
       </c>
     </row>
@@ -3548,11 +3110,6 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="inlineStr">
@@ -3567,51 +3124,45 @@
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>任务 id</t>
+          <t>任务id</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>Remind 匹配 step_id</t>
+          <t>NPC CharacterKey</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>递交目标 obj_id</t>
+          <t>Hub入口对话</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>NPC CharacterKey</t>
+          <t>Hub选项文案</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>对话角色</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
         <is>
-          <t>对话 id</t>
+          <t>接取成功对话</t>
         </is>
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Hub 选项文案</t>
+          <t>接取失败对话</t>
         </is>
       </c>
       <c r="J4" s="0" t="inlineStr">
         <is>
-          <t>显示条件</t>
-        </is>
-      </c>
-      <c r="K4" s="0" t="inlineStr">
-        <is>
-          <t>排序优先级</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
+          <t>开放条件(世界/任务门槛)</t>
+        </is>
+      </c>
+    </row>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>100</v>
@@ -3619,1121 +3170,1388 @@
       <c r="C6" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="D6" s="0" t="n"/>
-      <c r="E6" s="0" t="n"/>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_first_aid</t>
+        </is>
+      </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G6" s="0" t="inlineStr">
-        <is>
-          <t>Accept</t>
-        </is>
+          <t>检查他的伤势。</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid</t>
+          <t>carlisle_accept_first_aid_ok</t>
         </is>
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t>检查他的伤势。</t>
+          <t>carlisle_accept_first_aid_fail</t>
         </is>
       </c>
       <c r="J6" s="0" t="inlineStr">
         <is>
           <t>CheckVariable,0,0,0,0,test_link_a.camp_done,0</t>
         </is>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="D7" s="0" t="n"/>
-      <c r="E7" s="0" t="n"/>
+        <v>301</v>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit</t>
+        </is>
+      </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G7" s="0" t="inlineStr">
-        <is>
-          <t>AcceptSuccess</t>
-        </is>
+          <t>先把附近的怪物清掉。</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="H7" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid_ok</t>
-        </is>
-      </c>
-      <c r="I7" s="0" t="n"/>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
+          <t>carlisle_accept_clear_exit_ok</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_clear_exit_fail</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,300,0,0,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="0" t="n">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C8" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="n"/>
+        <v>302</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher</t>
+        </is>
+      </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G8" s="0" t="inlineStr">
-        <is>
-          <t>AcceptFail</t>
-        </is>
+          <t>做个能带他离开的东西。</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>10</v>
       </c>
       <c r="H8" s="0" t="inlineStr">
         <is>
-          <t>carlisle_accept_first_aid_fail</t>
-        </is>
-      </c>
-      <c r="I8" s="0" t="n"/>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
+          <t>carlisle_accept_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="I8" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_accept_stretcher_fail</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="inlineStr">
+        <is>
+          <t>TaskFinish,301,0,0,0,0,0</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="0" t="n">
+        <v>143</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>213</v>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>home_vera</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>问她水盆里的旧影。</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_ok</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_accept_fail</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>quest_id</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>step_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dialog_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>option_text</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>require_objective_dialog_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>show_cond</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>(list#sep=;),QuestDialogShowCond</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>任务id</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>匹配step</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>NPC CharacterKey</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>提醒对话</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hub选项文案</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>需先触发的ObjectiveDialog.id(0=无)</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>显示条件(任务对话状态)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="B6" t="n">
         <v>103</v>
       </c>
+      <c r="C6" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>300_s1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>carlisle_remind_first_aid</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>我该怎么稳定他的伤势？</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>113</v>
+      </c>
+      <c r="C7" t="n">
+        <v>301</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>301_s1</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>carlisle_remind_clear_exit</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>退路还不安全。</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>10</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>123</v>
+      </c>
+      <c r="C8" t="n">
+        <v>302</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>302_s1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>carlisle_remind_stretcher</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>还需要能固定他的材料。</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>129</v>
+      </c>
+      <c r="C9" t="n">
+        <v>203</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>203_s1</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>火堆还缺什么？</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>131</v>
+      </c>
+      <c r="C10" t="n">
+        <v>204</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>204_s1</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>灰露草棚要怎么处理？</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>134</v>
+      </c>
+      <c r="C11" t="n">
+        <v>206</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>206_s1</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>村外的路标怎么补？</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>137</v>
+      </c>
+      <c r="C12" t="n">
+        <v>208</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>208_s1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>需要带回什么样本？</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>139</v>
+      </c>
+      <c r="C13" t="n">
+        <v>211</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>211_s1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>forest_quest_211_remind</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>北路的花露有什么特征？</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>141</v>
+      </c>
+      <c r="C14" t="n">
+        <v>212</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>212_s1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>forest_quest_212_remind</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>森林之心究竟是什么？</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>146</v>
+      </c>
+      <c r="C15" t="n">
+        <v>213</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>213_s1</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>home_vera</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>vera_dream_remind</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>关于那个反复出现的梦……</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>quest_id</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>obj_id</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>entry_dialog_id</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>option_text</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>priority</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>once</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>success_dialog_id</t>
+        </is>
+      </c>
+      <c r="K1" s="0" t="inlineStr">
+        <is>
+          <t>fail_dialog_id</t>
+        </is>
+      </c>
+      <c r="L1" s="0" t="inlineStr">
+        <is>
+          <t>show_cond</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H2" s="0" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="I2" s="0" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="J2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" s="0" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="L2" s="0" t="inlineStr">
+        <is>
+          <t>(list#sep=;),QuestDialogShowCond</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="0" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="H3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="J3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="K3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="L3" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="0" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>任务id</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>目标obj_id</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>NPC CharacterKey</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>Hub入口对话</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr">
+        <is>
+          <t>Hub选项文案</t>
+        </is>
+      </c>
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>优先级</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>是否仅触发一次</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="inlineStr">
+        <is>
+          <t>成功对话</t>
+        </is>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>失败对话</t>
+        </is>
+      </c>
+      <c r="L4" s="0" t="inlineStr">
+        <is>
+          <t>显示条件(任务对话状态)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="0" t="n">
+        <v>104</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>300_s2_Main</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_entry</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr">
+        <is>
+          <t>给他做临时包扎。</t>
+        </is>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_ok</t>
+        </is>
+      </c>
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_first_aid_fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="0" t="n">
+        <v>124</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>302</v>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>302_s2_Main</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_entry</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr">
+        <is>
+          <t>把简易担架固定好。</t>
+        </is>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_ok</t>
+        </is>
+      </c>
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>carlisle_submit_stretcher_fail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="n">
+        <v>127</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>201</v>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>201_s1_Main</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr">
+        <is>
+          <t>到火堆边谈谈。</t>
+        </is>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="n">
+        <v>128</v>
+      </c>
       <c r="C9" s="0" t="n">
-        <v>300</v>
+        <v>202</v>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>300_s1</t>
-        </is>
-      </c>
-      <c r="E9" s="0" t="n"/>
-      <c r="F9" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>202_s1_Main</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H9" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_remind_first_aid</t>
-        </is>
-      </c>
-      <c r="I9" s="0" t="inlineStr">
-        <is>
-          <t>我该怎么稳定他的伤势？</t>
-        </is>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>10</v>
+          <t>确认幸存者人数。</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="D10" s="0" t="n"/>
+        <v>203</v>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>203_s2_Main</t>
+        </is>
+      </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
-        </is>
-      </c>
-      <c r="F10" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="H10" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_first_aid_entry</t>
-        </is>
-      </c>
-      <c r="I10" s="0" t="inlineStr">
-        <is>
-          <t>给他做临时包扎。</t>
-        </is>
-      </c>
-      <c r="K10" s="0" t="n">
+          <t>把木料交给他。</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="n">
         <v>20</v>
+      </c>
+      <c r="I10" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="n">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="D11" s="0" t="n"/>
+        <v>204</v>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>204_s2_Main</t>
+        </is>
+      </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
-        </is>
-      </c>
-      <c r="F11" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>home_merchant</t>
         </is>
       </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
-          <t>FulfillSuccess</t>
-        </is>
-      </c>
-      <c r="H11" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_first_aid_ok</t>
-        </is>
-      </c>
-      <c r="I11" s="0" t="n"/>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
+          <t>把灰露草送过去。</t>
+        </is>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I11" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="n">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>300</v>
-      </c>
-      <c r="D12" s="0" t="n"/>
+        <v>205</v>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>205_s1_Main</t>
+        </is>
+      </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>300_s2_Main</t>
-        </is>
-      </c>
-      <c r="F12" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G12" s="0" t="inlineStr">
         <is>
-          <t>FulfillFail</t>
-        </is>
-      </c>
-      <c r="H12" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_first_aid_fail</t>
-        </is>
-      </c>
-      <c r="I12" s="0" t="n"/>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
+          <t>确认临时住处已整理。</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I12" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="n">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C13" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D13" s="0" t="n"/>
-      <c r="E13" s="0" t="n"/>
-      <c r="F13" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+        <v>206</v>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>206_s2_Main</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G13" s="0" t="inlineStr">
         <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="H13" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit</t>
-        </is>
-      </c>
-      <c r="I13" s="0" t="inlineStr">
-        <is>
-          <t>先把附近的怪物清掉。</t>
-        </is>
-      </c>
-      <c r="J13" s="0" t="inlineStr">
-        <is>
-          <t>TaskFinish,300,0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>10</v>
+          <t>把路标材料交给他。</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="n">
-        <v>111</v>
+        <v>136</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D14" s="0" t="n"/>
-      <c r="E14" s="0" t="n"/>
-      <c r="F14" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+        <v>207</v>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>207_s1_Main</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G14" s="0" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
-        </is>
-      </c>
-      <c r="H14" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit_ok</t>
-        </is>
-      </c>
-      <c r="I14" s="0" t="n"/>
-      <c r="K14" s="0" t="n">
-        <v>0</v>
+          <t>开放村东通路。</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="I14" s="0" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="n">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="C15" s="0" t="n">
-        <v>301</v>
-      </c>
-      <c r="D15" s="0" t="n"/>
-      <c r="E15" s="0" t="n"/>
-      <c r="F15" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
+        <v>208</v>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>208_s2_Main</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
         </is>
       </c>
       <c r="G15" s="0" t="inlineStr">
         <is>
-          <t>AcceptFail</t>
-        </is>
-      </c>
-      <c r="H15" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_clear_exit_fail</t>
-        </is>
-      </c>
-      <c r="I15" s="0" t="n"/>
-      <c r="K15" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1">
+          <t>把雾线样本交给埃蒙。</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I15" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="0" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="C16" s="0" t="n">
-        <v>301</v>
+        <v>211</v>
       </c>
       <c r="D16" s="0" t="inlineStr">
         <is>
-          <t>301_s1</t>
-        </is>
-      </c>
-      <c r="E16" s="0" t="n"/>
+          <t>211_s2_Main</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
       <c r="F16" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>forest_quest_211_fulfill</t>
         </is>
       </c>
       <c r="G16" s="0" t="inlineStr">
         <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H16" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_remind_clear_exit</t>
-        </is>
-      </c>
-      <c r="I16" s="0" t="inlineStr">
-        <is>
-          <t>退路还不安全。</t>
-        </is>
-      </c>
-      <c r="K16" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" s="1">
+          <t>交出两份森林花露。</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I16" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="B17" s="0" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="C17" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D17" s="0" t="n"/>
-      <c r="E17" s="0" t="n"/>
+        <v>212</v>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>212_s2_Main</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>home_elder</t>
+        </is>
+      </c>
       <c r="F17" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>forest_quest_212_fulfill</t>
         </is>
       </c>
       <c r="G17" s="0" t="inlineStr">
         <is>
-          <t>Accept</t>
-        </is>
-      </c>
-      <c r="H17" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher</t>
-        </is>
-      </c>
-      <c r="I17" s="0" t="inlineStr">
-        <is>
-          <t>做个能带他离开的东西。</t>
-        </is>
-      </c>
-      <c r="J17" s="0" t="inlineStr">
-        <is>
-          <t>TaskFinish,301,0,0,0,0,0</t>
-        </is>
-      </c>
-      <c r="K17" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" s="1">
+          <t>汇报森林之心的反应。</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="0" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="B18" s="0" t="n">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="C18" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D18" s="0" t="n"/>
-      <c r="E18" s="0" t="n"/>
+        <v>213</v>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>213_s2_Main</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>home_vera</t>
+        </is>
+      </c>
       <c r="F18" s="0" t="inlineStr">
         <is>
-          <t>carlisle</t>
+          <t>vera_dream_after</t>
         </is>
       </c>
       <c r="G18" s="0" t="inlineStr">
         <is>
-          <t>AcceptSuccess</t>
-        </is>
-      </c>
-      <c r="H18" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher_ok</t>
-        </is>
-      </c>
-      <c r="I18" s="0" t="n"/>
-      <c r="K18" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" s="1">
-      <c r="B19" s="0" t="n">
-        <v>122</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D19" s="0" t="n"/>
-      <c r="E19" s="0" t="n"/>
-      <c r="F19" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G19" s="0" t="inlineStr">
-        <is>
-          <t>AcceptFail</t>
-        </is>
-      </c>
-      <c r="H19" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_accept_stretcher_fail</t>
-        </is>
-      </c>
-      <c r="I19" s="0" t="n"/>
-      <c r="K19" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="1">
-      <c r="B20" s="0" t="n">
-        <v>123</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D20" s="0" t="inlineStr">
-        <is>
-          <t>302_s1</t>
-        </is>
-      </c>
-      <c r="E20" s="0" t="n"/>
-      <c r="F20" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G20" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H20" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_remind_stretcher</t>
-        </is>
-      </c>
-      <c r="I20" s="0" t="inlineStr">
-        <is>
-          <t>还需要能固定他的材料。</t>
-        </is>
-      </c>
-      <c r="K20" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21" s="1">
-      <c r="B21" s="0" t="n">
-        <v>124</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D21" s="0" t="n"/>
-      <c r="E21" s="0" t="inlineStr">
-        <is>
-          <t>302_s2_Main</t>
-        </is>
-      </c>
-      <c r="F21" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G21" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="H21" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_entry</t>
-        </is>
-      </c>
-      <c r="I21" s="0" t="inlineStr">
-        <is>
-          <t>把简易担架固定好。</t>
-        </is>
-      </c>
-      <c r="K21" s="0" t="n">
+          <t>告诉她梦中的结果。</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" s="1">
-      <c r="B22" s="0" t="n">
-        <v>125</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D22" s="0" t="n"/>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>302_s2_Main</t>
-        </is>
-      </c>
-      <c r="F22" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>FulfillSuccess</t>
-        </is>
-      </c>
-      <c r="H22" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_ok</t>
-        </is>
-      </c>
-      <c r="I22" s="0" t="n"/>
-      <c r="K22" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="1">
-      <c r="B23" s="0" t="n">
-        <v>126</v>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>302</v>
-      </c>
-      <c r="D23" s="0" t="n"/>
-      <c r="E23" s="0" t="inlineStr">
-        <is>
-          <t>302_s2_Main</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>carlisle</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>FulfillFail</t>
-        </is>
-      </c>
-      <c r="H23" s="0" t="inlineStr">
-        <is>
-          <t>carlisle_submit_stretcher_fail</t>
-        </is>
-      </c>
-      <c r="I23" s="0" t="n"/>
-      <c r="K23" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" s="1">
-      <c r="B24" s="0" t="n">
-        <v>127</v>
-      </c>
-      <c r="C24" s="0" t="n">
-        <v>201</v>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
-        <is>
-          <t>201_s1_Main</t>
-        </is>
-      </c>
-      <c r="F24" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G24" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I24" s="0" t="inlineStr">
-        <is>
-          <t>到火堆边谈谈。</t>
-        </is>
-      </c>
-      <c r="K24" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" s="1">
-      <c r="B25" s="0" t="n">
-        <v>128</v>
-      </c>
-      <c r="C25" s="0" t="n">
-        <v>202</v>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
-        <is>
-          <t>202_s1_Main</t>
-        </is>
-      </c>
-      <c r="F25" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I25" s="0" t="inlineStr">
-        <is>
-          <t>确认幸存者人数。</t>
-        </is>
-      </c>
-      <c r="K25" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" s="1">
-      <c r="B26" s="0" t="n">
-        <v>129</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>203</v>
-      </c>
-      <c r="D26" s="0" t="inlineStr">
-        <is>
-          <t>203_s1</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>home_merchant</t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="I26" s="0" t="inlineStr">
-        <is>
-          <t>火堆还缺什么？</t>
-        </is>
-      </c>
-      <c r="K26" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" s="1">
-      <c r="B27" s="0" t="n">
-        <v>130</v>
-      </c>
-      <c r="C27" s="0" t="n">
-        <v>203</v>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
-        <is>
-          <t>203_s2_Main</t>
-        </is>
-      </c>
-      <c r="F27" s="0" t="inlineStr">
-        <is>
-          <t>home_merchant</t>
-        </is>
-      </c>
-      <c r="G27" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I27" s="0" t="inlineStr">
-        <is>
-          <t>把木料交给他。</t>
-        </is>
-      </c>
-      <c r="K27" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" s="1">
-      <c r="B28" s="0" t="n">
-        <v>131</v>
-      </c>
-      <c r="C28" s="0" t="n">
-        <v>204</v>
-      </c>
-      <c r="D28" s="0" t="inlineStr">
-        <is>
-          <t>204_s1</t>
-        </is>
-      </c>
-      <c r="F28" s="0" t="inlineStr">
-        <is>
-          <t>home_merchant</t>
-        </is>
-      </c>
-      <c r="G28" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="I28" s="0" t="inlineStr">
-        <is>
-          <t>灰露草棚要怎么处理？</t>
-        </is>
-      </c>
-      <c r="K28" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="29" s="1">
-      <c r="B29" s="0" t="n">
-        <v>132</v>
-      </c>
-      <c r="C29" s="0" t="n">
-        <v>204</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
-        <is>
-          <t>204_s2_Main</t>
-        </is>
-      </c>
-      <c r="F29" s="0" t="inlineStr">
-        <is>
-          <t>home_merchant</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I29" s="0" t="inlineStr">
-        <is>
-          <t>把灰露草送过去。</t>
-        </is>
-      </c>
-      <c r="K29" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" s="1">
-      <c r="B30" s="0" t="n">
-        <v>133</v>
-      </c>
-      <c r="C30" s="0" t="n">
-        <v>205</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>205_s1_Main</t>
-        </is>
-      </c>
-      <c r="F30" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G30" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I30" s="0" t="inlineStr">
-        <is>
-          <t>确认临时住处已整理。</t>
-        </is>
-      </c>
-      <c r="K30" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="31" s="1">
-      <c r="B31" s="0" t="n">
-        <v>134</v>
-      </c>
-      <c r="C31" s="0" t="n">
-        <v>206</v>
-      </c>
-      <c r="D31" s="0" t="inlineStr">
-        <is>
-          <t>206_s1</t>
-        </is>
-      </c>
-      <c r="F31" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G31" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="I31" s="0" t="inlineStr">
-        <is>
-          <t>村外的路标怎么补？</t>
-        </is>
-      </c>
-      <c r="K31" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32" s="1">
-      <c r="B32" s="0" t="n">
-        <v>135</v>
-      </c>
-      <c r="C32" s="0" t="n">
-        <v>206</v>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
-        <is>
-          <t>206_s2_Main</t>
-        </is>
-      </c>
-      <c r="F32" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G32" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I32" s="0" t="inlineStr">
-        <is>
-          <t>把路标材料交给他。</t>
-        </is>
-      </c>
-      <c r="K32" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" s="1">
-      <c r="B33" s="0" t="n">
-        <v>136</v>
-      </c>
-      <c r="C33" s="0" t="n">
-        <v>207</v>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
-        <is>
-          <t>207_s1_Main</t>
-        </is>
-      </c>
-      <c r="F33" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G33" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I33" s="0" t="inlineStr">
-        <is>
-          <t>开放村东通路。</t>
-        </is>
-      </c>
-      <c r="K33" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" s="1">
-      <c r="B34" s="0" t="n">
-        <v>137</v>
-      </c>
-      <c r="C34" s="0" t="n">
-        <v>208</v>
-      </c>
-      <c r="D34" s="0" t="inlineStr">
-        <is>
-          <t>208_s1</t>
-        </is>
-      </c>
-      <c r="F34" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G34" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="I34" s="0" t="inlineStr">
-        <is>
-          <t>需要带回什么样本？</t>
-        </is>
-      </c>
-      <c r="K34" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" s="1">
-      <c r="B35" s="0" t="n">
-        <v>138</v>
-      </c>
-      <c r="C35" s="0" t="n">
-        <v>208</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>208_s2_Main</t>
-        </is>
-      </c>
-      <c r="F35" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G35" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="I35" s="0" t="inlineStr">
-        <is>
-          <t>把雾线样本交给埃蒙。</t>
-        </is>
-      </c>
-      <c r="K35" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" s="1">
-      <c r="B36" s="0" t="n">
-        <v>139</v>
-      </c>
-      <c r="C36" s="0" t="n">
-        <v>211</v>
-      </c>
-      <c r="D36" s="0" t="inlineStr">
-        <is>
-          <t>211_s1</t>
-        </is>
-      </c>
-      <c r="E36" s="0" t="n"/>
-      <c r="F36" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G36" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H36" s="0" t="inlineStr">
-        <is>
-          <t>forest_quest_211_remind</t>
-        </is>
-      </c>
-      <c r="I36" s="0" t="inlineStr">
-        <is>
-          <t>北路的花露有什么特征？</t>
-        </is>
-      </c>
-      <c r="K36" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" s="1">
-      <c r="B37" s="0" t="n">
-        <v>140</v>
-      </c>
-      <c r="C37" s="0" t="n">
-        <v>211</v>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
-        <is>
-          <t>211_s2_Main</t>
-        </is>
-      </c>
-      <c r="F37" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G37" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="H37" s="0" t="inlineStr">
-        <is>
-          <t>forest_quest_211_fulfill</t>
-        </is>
-      </c>
-      <c r="I37" s="0" t="inlineStr">
-        <is>
-          <t>交出两份森林花露。</t>
-        </is>
-      </c>
-      <c r="K37" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="38" s="1">
-      <c r="B38" s="0" t="n">
-        <v>141</v>
-      </c>
-      <c r="C38" s="0" t="n">
-        <v>212</v>
-      </c>
-      <c r="D38" s="0" t="inlineStr">
-        <is>
-          <t>212_s1</t>
-        </is>
-      </c>
-      <c r="E38" s="0" t="n"/>
-      <c r="F38" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G38" s="0" t="inlineStr">
-        <is>
-          <t>Remind</t>
-        </is>
-      </c>
-      <c r="H38" s="0" t="inlineStr">
-        <is>
-          <t>forest_quest_212_remind</t>
-        </is>
-      </c>
-      <c r="I38" s="0" t="inlineStr">
-        <is>
-          <t>森林之心究竟是什么？</t>
-        </is>
-      </c>
-      <c r="K38" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" s="1">
-      <c r="B39" s="0" t="n">
-        <v>142</v>
-      </c>
-      <c r="C39" s="0" t="n">
-        <v>212</v>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>212_s2_Main</t>
-        </is>
-      </c>
-      <c r="F39" s="0" t="inlineStr">
-        <is>
-          <t>home_elder</t>
-        </is>
-      </c>
-      <c r="G39" s="0" t="inlineStr">
-        <is>
-          <t>Fulfill</t>
-        </is>
-      </c>
-      <c r="H39" s="0" t="inlineStr">
-        <is>
-          <t>forest_quest_212_fulfill</t>
-        </is>
-      </c>
-      <c r="I39" s="0" t="inlineStr">
-        <is>
-          <t>汇报森林之心的反应。</t>
-        </is>
-      </c>
-      <c r="J39" s="0" t="n"/>
-      <c r="K39" s="0" t="n">
-        <v>20</v>
+      <c r="I18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>vera_dream_complete</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -397,7 +397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.625" customWidth="1" style="1" min="2" max="2"/>
@@ -759,7 +759,7 @@
       </c>
       <c r="H6" s="0" t="inlineStr">
         <is>
-          <t>1,101,0,0,0,0,0</t>
+          <t>1,200,0,0,0,0,0</t>
         </is>
       </c>
       <c r="J6" s="0" t="b">
@@ -2622,6 +2622,54 @@
         <v>0</v>
       </c>
       <c r="L71" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_request</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_request</t>
+        </is>
+      </c>
+      <c r="J72" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_return</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_return</t>
+        </is>
+      </c>
+      <c r="J73" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3337,531 +3385,530 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>quest_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>step_id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>character_key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>dialog_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>option_text</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="0" t="inlineStr">
         <is>
           <t>priority</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="0" t="inlineStr">
         <is>
           <t>require_objective_dialog_id</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="0" t="inlineStr">
         <is>
           <t>show_cond</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="0" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="0" t="inlineStr">
         <is>
           <t>(list#sep=;),QuestDialogShowCond</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>任务id</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>匹配step</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>NPC CharacterKey</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>提醒对话</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>Hub选项文案</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>需先触发的ObjectiveDialog.id(0=无)</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="0" t="inlineStr">
         <is>
           <t>显示条件(任务对话状态)</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
-      <c r="B6" t="n">
+      <c r="B6" s="0" t="n">
         <v>103</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>300_s1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>carlisle</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_first_aid</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>我该怎么稳定他的伤势？</t>
         </is>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
+      <c r="B7" s="0" t="n">
         <v>113</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="0" t="n">
         <v>301</v>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>301_s1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>carlisle</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_clear_exit</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>退路还不安全。</t>
         </is>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
+      <c r="B8" s="0" t="n">
         <v>123</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="0" t="n">
         <v>302</v>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>302_s1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>carlisle</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>carlisle_remind_stretcher</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>还需要能固定他的材料。</t>
         </is>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
+      <c r="B9" s="0" t="n">
         <v>129</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="0" t="n">
         <v>203</v>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>203_s1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>火堆还缺什么？</t>
         </is>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="0" t="n">
         <v>131</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="0" t="n">
         <v>204</v>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>204_s1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>灰露草棚要怎么处理？</t>
         </is>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="0" t="n">
         <v>134</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="0" t="n">
         <v>206</v>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>206_s1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>村外的路标怎么补？</t>
         </is>
       </c>
-      <c r="H11" t="n">
+      <c r="H11" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="0" t="n">
         <v>137</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="0" t="n">
         <v>208</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>208_s1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>需要带回什么样本？</t>
         </is>
       </c>
-      <c r="H12" t="n">
+      <c r="H12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="0" t="n">
         <v>139</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="0" t="n">
         <v>211</v>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>211_s1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>forest_quest_211_remind</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>北路的花露有什么特征？</t>
         </is>
       </c>
-      <c r="H13" t="n">
+      <c r="H13" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="0" t="n">
         <v>141</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="0" t="n">
         <v>212</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>212_s1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>home_elder</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>forest_quest_212_remind</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>森林之心究竟是什么？</t>
         </is>
       </c>
-      <c r="H14" t="n">
+      <c r="H14" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="0" t="n">
         <v>146</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="0" t="n">
         <v>213</v>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>213_s1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>home_vera</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>vera_dream_remind</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>关于那个反复出现的梦……</t>
         </is>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="0" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3876,7 +3923,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4554,6 +4601,74 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>148</v>
+      </c>
+      <c r="C19" t="n">
+        <v>214</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>214_s1_Main</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_request</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>和萨赫尔谈谈。</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>20</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>149</v>
+      </c>
+      <c r="C20" t="n">
+        <v>214</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>214_s3_Main</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>home_merchant</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>sahel_kitchen_return</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>把厨具交还给萨赫尔。</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Config/Datas/dialog.xlsx
+++ b/Config/Datas/dialog.xlsx
@@ -397,7 +397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="28.625" customWidth="1" style="1" min="2" max="2"/>
@@ -2626,52 +2626,176 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_request</t>
         </is>
       </c>
-      <c r="D72" t="b">
-        <v>0</v>
-      </c>
-      <c r="E72" t="b">
-        <v>0</v>
-      </c>
-      <c r="F72" t="inlineStr">
+      <c r="D72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_request</t>
         </is>
       </c>
-      <c r="J72" t="b">
-        <v>0</v>
-      </c>
-      <c r="L72" t="n">
+      <c r="J72" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L72" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_return</t>
         </is>
       </c>
-      <c r="D73" t="b">
-        <v>0</v>
-      </c>
-      <c r="E73" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" t="inlineStr">
+      <c r="D73" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E73" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_return</t>
         </is>
       </c>
-      <c r="J73" t="b">
-        <v>0</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
-      </c>
+      <c r="J73" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="L73" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>village_herbalist_01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+      <c r="E74" t="b">
+        <v>0</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>village_herbalist_01</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="b">
+        <v>0</v>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="n">
+        <v>10</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>village_herbalist_request</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+      <c r="E75" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>village_herbalist_request</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="b">
+        <v>0</v>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="n">
+        <v>10</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>village_herbalist_remind</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" t="b">
+        <v>0</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>village_herbalist_remind</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="b">
+        <v>0</v>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>village_herbalist_return</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" t="b">
+        <v>0</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>village_herbalist_return</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="b">
+        <v>0</v>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="n">
+        <v>10</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2685,7 +2809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="13" customWidth="1" style="1" min="2" max="2"/>
@@ -2973,6 +3097,26 @@
       <c r="E11" s="0" t="n">
         <v>10</v>
       </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>900</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>village_herbalist_01</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3000,7 +3144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3211,6 +3355,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>100</v>
@@ -3369,6 +3514,39 @@
           <t>vera_dream_accept_fail</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2150</v>
+      </c>
+      <c r="C10" t="n">
+        <v>215</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>village_herbalist_request</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>买一份草药敗剂</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>village_herbalist_request</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3381,7 +3559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3592,6 +3770,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>103</v>
@@ -3911,6 +4090,41 @@
       <c r="I15" s="0" t="n">
         <v>0</v>
       </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>2151</v>
+      </c>
+      <c r="C16" t="n">
+        <v>215</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>215_s2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>village_herbalist_remind</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>该买哪种药？</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3923,7 +4137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4174,6 +4388,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="0" t="n">
         <v>104</v>
@@ -4602,72 +4817,146 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>148</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="0" t="n">
         <v>214</v>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>214_s1_Main</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_request</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>和萨赫尔谈谈。</t>
         </is>
       </c>
-      <c r="H19" t="n">
+      <c r="H19" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I19" t="b">
+      <c r="I19" s="0" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>149</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="0" t="n">
         <v>214</v>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>214_s3_Main</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>home_merchant</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>sahel_kitchen_return</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>把厨具交还给萨赫尔。</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="0" t="n">
         <v>20</v>
       </c>
-      <c r="I20" t="b">
+      <c r="I20" s="0" t="b">
         <v>1</v>
       </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>2152</v>
+      </c>
+      <c r="C21" t="n">
+        <v>215</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>215_s1_Main</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>village_herbalist_request</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>和他谈谈</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>2153</v>
+      </c>
+      <c r="C22" t="n">
+        <v>215</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>215_s3_Main</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>village_herbalist</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>village_herbalist_return</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>交出草药敷剂</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
